--- a/templates/外汇新闻印尼/scripts.xlsx
+++ b/templates/外汇新闻印尼/scripts.xlsx
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quickpro_vs_foreximf</t>
+          <t>broker_radar_2negara</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QuickPro itu broker baru, atau cuma ganti nama dari ForexIMF? Dan kenapa setelah rebranding justru muncul banyak pertanyaan? Sejak Februari 2026, ForexIMF resmi berganti nama menjadi QuickPro. Perusahaan menyebut ini hanya perubahan identitas, tanpa mengubah legalitas maupun layanan. Tapi di sisi lain, muncul beberapa hal yang jadi perhatian trader. Mulai dari status verifikasi lisensi yang masih menjadi catatan di WikiFX, pertanyaan soal domain resmi QuickPro, beragam ulasan pengguna di Google Play Store, hingga laporan dari pengguna melalui fitur Paparan WikiFX. Semua itu belum tentu membuktikan adanya pelanggaran, tapi cukup menjadi alasan untuk melakukan riset lebih dalam. Jadi, QuickPro aman atau tidak? Jawabannya ada di hasil verifikasi kamu sendiri. Selalu cek legalitas, baca review pengguna, dan teliti sebelum memilih broker. Jangan sampai salah pilih!</t>
+          <t>Buat kalian yang main forex, hati-hati! Broker Trading Pro sekarang lagi jadi sorotan tajam di dunia trading internasional! Nggak main-main, broker ini masuk radar dua regulator sekaligus. FCA Inggris resmi memasukkannya ke daftar warning list, dan di Indonesia, BAPPEBTI sudah dua kali memblokir situs mereka! Bukan cuma soal izin, investigasi lapangan dari WikiFX juga menemukan kejanggalan pada alamat kantor operasionalnya yang sulit diverifikasi. Parahnya lagi, mulai muncul rentetan keluhan dari para trader terkait lambatnya proses withdrawal atau penarikan dana, hingga masalah teknis akun. Ingat, leverage tinggi dan bonus besar nggak ada gunanya kalau dana kalian nggak aman. Selalu cek legalitas broker sebelum deposit. Jangan sampai menyesal kemudian!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>forex broker rebranding license verification app review</t>
+          <t>forex broker warning regulator office complaint withdrawal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,22 +473,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stop_loss_spread</t>
+          <t>ancaman_15tahun_ponzi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pernah nggak? Bangun pagi, buka MT4, eh Stop Loss sudah kena. Padahal arah harga akhirnya sesuai analisismu. Broker curang atau ada yang lain? Belum tentu broker nakal. Penyebab paling sering adalah spread melebar. Ini biasanya terjadi saat rollover sekitar jam 4 sampai 5 pagi WIB atau ketika berita besar seperti NFP dan inflasi dirilis. Di momen itu, likuiditas pasar menipis karena banyak bank besar menarik order. Akibatnya spread yang tadinya kecil bisa melebar berkali-kali lipat dan Stop Loss yang terlalu dekat ikut tersentuh. Supaya lebih aman, hindari pasang SL terlalu mepet, jangan gunakan lot berlebihan, dan waspadai jam rollover maupun jadwal berita penting. Sebelum memilih broker, cek dulu regulasi dan reputasinya di WikiFX agar terhindar dari broker yang memperlebar spread secara tidak wajar.</t>
+          <t>Hati-hati! Risiko terbesar dalam forex itu kadang bukan dari pasarnya, tapi dari orang yang pegang uang kamu! Di Australia, seorang mantan direktur baru saja mengaku bersalah setelah membawa kabur dana investor senilai 1,5 juta Dolar Australia atau sekitar 15 miliar Rupiah! Janjinya uang itu dipakai untuk trading forex. Tapi faktanya? Malah dipakai buat kebutuhan pribadi dan bayar investor lain dengan pola mirip Skema Ponzi! Pelajaran penting buat kita di Indonesia yang sering tergiur embel-embel robot trading, copy trading, atau program profit sharing. Ingat, sebelum kejar profit, pastikan legalitasnya jelas dan transparan. Jangan sampai uangmu hilang sebelum masuk pasar!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>forex trading stop loss spread chart MT4 news volatility</t>
+          <t>forex investment fraud court director money ponzi australia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANALISIS FOREX</t>
+          <t>PERINGATAN PENIPUAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
